--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA KHUSUS.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA KHUSUS.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,147 +429,147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Hasil Pendataan PPL</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Persentase Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA KHUSUS.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA KHUSUS.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,147 +417,147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Hasil Pendataan PPL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Persentase Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA KHUSUS.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA KHUSUS.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,147 +429,147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Hasil Pendataan PPL</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Persentase Bangunan Keluarga Khusus Didata</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>PENDATAAN K1 - Persentase Bangunan Keluarga Khusus Didata</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -584,76 +596,76 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>643</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>2752</v>
+        <v>3545</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="I2" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="O2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P2" t="n">
-        <v>4258</v>
+        <v>4454</v>
       </c>
       <c r="Q2" t="n">
-        <v>3560</v>
+        <v>4424</v>
       </c>
       <c r="R2" t="n">
-        <v>643</v>
+        <v>28</v>
       </c>
       <c r="S2" t="n">
-        <v>2754</v>
+        <v>3533</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="U2" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>5</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4</v>
       </c>
       <c r="Y2" t="n">
         <v>3</v>
       </c>
       <c r="Z2" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="AA2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB2" t="n">
-        <v>4258</v>
+        <v>4453</v>
       </c>
       <c r="AC2" t="n">
-        <v>3560</v>
+        <v>4423</v>
       </c>
     </row>
     <row r="3">
@@ -677,19 +689,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>857</v>
+        <v>1112</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -701,31 +713,31 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>1490</v>
+        <v>1513</v>
       </c>
       <c r="Q3" t="n">
-        <v>1107</v>
+        <v>1356</v>
       </c>
       <c r="R3" t="n">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="S3" t="n">
-        <v>857</v>
+        <v>1112</v>
       </c>
       <c r="T3" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="U3" t="n">
-        <v>199</v>
+        <v>105</v>
       </c>
       <c r="V3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -737,16 +749,16 @@
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1490</v>
+        <v>1513</v>
       </c>
       <c r="AC3" t="n">
-        <v>1107</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="4">
@@ -761,85 +773,85 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>112</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5543</v>
+      </c>
+      <c r="H4" t="n">
+        <v>389</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J4" t="n">
+        <v>133</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>592</v>
+      </c>
+      <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>957</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4368</v>
-      </c>
-      <c r="H4" t="n">
-        <v>399</v>
-      </c>
-      <c r="I4" t="n">
-        <v>100</v>
-      </c>
-      <c r="J4" t="n">
-        <v>73</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>588</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
       <c r="P4" t="n">
-        <v>6487</v>
+        <v>6795</v>
       </c>
       <c r="Q4" t="n">
-        <v>5430</v>
+        <v>6662</v>
       </c>
       <c r="R4" t="n">
-        <v>959</v>
+        <v>113</v>
       </c>
       <c r="S4" t="n">
-        <v>4368</v>
+        <v>5543</v>
       </c>
       <c r="T4" t="n">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="U4" t="n">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="V4" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>6487</v>
+        <v>6795</v>
       </c>
       <c r="AC4" t="n">
-        <v>5430</v>
+        <v>6661</v>
       </c>
     </row>
     <row r="5">
@@ -863,76 +875,76 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2276</v>
+        <v>3010</v>
       </c>
       <c r="H5" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>3306</v>
+        <v>3521</v>
       </c>
       <c r="Q5" t="n">
-        <v>2924</v>
+        <v>3521</v>
       </c>
       <c r="R5" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2276</v>
+        <v>3010</v>
       </c>
       <c r="T5" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="AA5" t="n">
         <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>3306</v>
+        <v>3521</v>
       </c>
       <c r="AC5" t="n">
-        <v>2923</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="6">
@@ -947,7 +959,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -956,76 +968,76 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>310</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>694</v>
+        <v>952</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" t="n">
         <v>16</v>
       </c>
-      <c r="J6" t="n">
-        <v>9</v>
-      </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>1158</v>
+        <v>1209</v>
       </c>
       <c r="Q6" t="n">
-        <v>832</v>
+        <v>1100</v>
       </c>
       <c r="R6" t="n">
-        <v>310</v>
+        <v>102</v>
       </c>
       <c r="S6" t="n">
-        <v>694</v>
+        <v>952</v>
       </c>
       <c r="T6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
+        <v>7</v>
+      </c>
+      <c r="V6" t="n">
         <v>16</v>
       </c>
-      <c r="V6" t="n">
-        <v>9</v>
-      </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="n">
         <v>7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1158</v>
+        <v>1209</v>
       </c>
       <c r="AC6" t="n">
-        <v>832</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
@@ -1040,7 +1052,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1049,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>644</v>
+        <v>912</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1073,28 +1085,28 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>1065</v>
+        <v>1133</v>
       </c>
       <c r="Q7" t="n">
-        <v>784</v>
+        <v>1086</v>
       </c>
       <c r="R7" t="n">
-        <v>280</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
-        <v>644</v>
+        <v>912</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1109,16 +1121,16 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="AA7" t="n">
         <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1065</v>
+        <v>1133</v>
       </c>
       <c r="AC7" t="n">
-        <v>784</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="8">
@@ -1142,76 +1154,76 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1630</v>
+        <v>745</v>
       </c>
       <c r="G8" t="n">
-        <v>2443</v>
+        <v>3557</v>
       </c>
       <c r="H8" t="n">
-        <v>289</v>
+        <v>205</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="J8" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="O8" t="n">
         <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>4810</v>
+        <v>5199</v>
       </c>
       <c r="Q8" t="n">
-        <v>3153</v>
+        <v>4402</v>
       </c>
       <c r="R8" t="n">
-        <v>1630</v>
+        <v>748</v>
       </c>
       <c r="S8" t="n">
-        <v>2443</v>
+        <v>3555</v>
       </c>
       <c r="T8" t="n">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="U8" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="V8" t="n">
-        <v>25</v>
+        <v>228</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AA8" t="n">
         <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>4810</v>
+        <v>5199</v>
       </c>
       <c r="AC8" t="n">
-        <v>3153</v>
+        <v>4399</v>
       </c>
     </row>
     <row r="9">
@@ -1235,76 +1247,76 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1980</v>
+        <v>742</v>
       </c>
       <c r="G9" t="n">
-        <v>3260</v>
+        <v>4117</v>
       </c>
       <c r="H9" t="n">
-        <v>296</v>
+        <v>780</v>
       </c>
       <c r="I9" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="J9" t="n">
-        <v>198</v>
+        <v>336</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>6348</v>
+        <v>6749</v>
       </c>
       <c r="Q9" t="n">
-        <v>4331</v>
+        <v>5894</v>
       </c>
       <c r="R9" t="n">
-        <v>1980</v>
+        <v>742</v>
       </c>
       <c r="S9" t="n">
-        <v>3260</v>
+        <v>4117</v>
       </c>
       <c r="T9" t="n">
-        <v>295</v>
+        <v>780</v>
       </c>
       <c r="U9" t="n">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="V9" t="n">
-        <v>198</v>
+        <v>335</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>577</v>
+        <v>625</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>6347</v>
+        <v>6749</v>
       </c>
       <c r="AC9" t="n">
-        <v>4330</v>
+        <v>5894</v>
       </c>
     </row>
     <row r="10">
@@ -1328,76 +1340,76 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2620</v>
+        <v>980</v>
       </c>
       <c r="G10" t="n">
-        <v>5034</v>
+        <v>6975</v>
       </c>
       <c r="H10" t="n">
-        <v>48</v>
+        <v>281</v>
       </c>
       <c r="I10" t="n">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="J10" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P10" t="n">
-        <v>8450</v>
+        <v>8991</v>
       </c>
       <c r="Q10" t="n">
-        <v>5652</v>
+        <v>7916</v>
       </c>
       <c r="R10" t="n">
-        <v>2620</v>
+        <v>981</v>
       </c>
       <c r="S10" t="n">
-        <v>5034</v>
+        <v>6975</v>
       </c>
       <c r="T10" t="n">
-        <v>48</v>
+        <v>280</v>
       </c>
       <c r="U10" t="n">
-        <v>176</v>
+        <v>95</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>542</v>
+        <v>580</v>
       </c>
       <c r="AA10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
-        <v>8448</v>
+        <v>8991</v>
       </c>
       <c r="AC10" t="n">
-        <v>5652</v>
+        <v>7915</v>
       </c>
     </row>
     <row r="11">
@@ -1412,7 +1424,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1421,76 +1433,76 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1416</v>
+        <v>432</v>
       </c>
       <c r="G11" t="n">
-        <v>3241</v>
+        <v>4389</v>
       </c>
       <c r="H11" t="n">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="I11" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J11" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
         <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>5361</v>
+        <v>5634</v>
       </c>
       <c r="Q11" t="n">
-        <v>3797</v>
+        <v>5057</v>
       </c>
       <c r="R11" t="n">
-        <v>1418</v>
+        <v>434</v>
       </c>
       <c r="S11" t="n">
-        <v>3241</v>
+        <v>4389</v>
       </c>
       <c r="T11" t="n">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="U11" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="V11" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X11" t="n">
         <v>6</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11" t="n">
-        <v>5361</v>
+        <v>5634</v>
       </c>
       <c r="AC11" t="n">
-        <v>3795</v>
+        <v>5055</v>
       </c>
     </row>
     <row r="12">
@@ -1514,22 +1526,22 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>751</v>
+        <v>174</v>
       </c>
       <c r="G12" t="n">
-        <v>1250</v>
+        <v>1652</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="I12" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="J12" t="n">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1538,34 +1550,34 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>2445</v>
+        <v>2485</v>
       </c>
       <c r="Q12" t="n">
-        <v>1608</v>
+        <v>2257</v>
       </c>
       <c r="R12" t="n">
-        <v>751</v>
+        <v>174</v>
       </c>
       <c r="S12" t="n">
-        <v>1248</v>
+        <v>1652</v>
       </c>
       <c r="T12" t="n">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="U12" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="V12" t="n">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X12" t="n">
         <v>7</v>
@@ -1574,16 +1586,16 @@
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="AA12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB12" t="n">
-        <v>2445</v>
+        <v>2485</v>
       </c>
       <c r="AC12" t="n">
-        <v>1608</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="13">
@@ -1607,76 +1619,76 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1393</v>
+        <v>149</v>
       </c>
       <c r="G13" t="n">
-        <v>7134</v>
+        <v>8976</v>
       </c>
       <c r="H13" t="n">
-        <v>54</v>
+        <v>152</v>
       </c>
       <c r="I13" t="n">
-        <v>147</v>
+        <v>58</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="O13" t="n">
         <v>14</v>
       </c>
       <c r="P13" t="n">
-        <v>9735</v>
+        <v>10379</v>
       </c>
       <c r="Q13" t="n">
-        <v>8195</v>
+        <v>10172</v>
       </c>
       <c r="R13" t="n">
-        <v>1394</v>
+        <v>149</v>
       </c>
       <c r="S13" t="n">
-        <v>7134</v>
+        <v>8976</v>
       </c>
       <c r="T13" t="n">
-        <v>54</v>
+        <v>151</v>
       </c>
       <c r="U13" t="n">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>969</v>
+        <v>983</v>
       </c>
       <c r="AA13" t="n">
         <v>14</v>
       </c>
       <c r="AB13" t="n">
-        <v>9735</v>
+        <v>10379</v>
       </c>
       <c r="AC13" t="n">
-        <v>8195</v>
+        <v>10171</v>
       </c>
     </row>
     <row r="14">
@@ -1700,13 +1712,13 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>891</v>
+        <v>1038</v>
       </c>
       <c r="H14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1718,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1730,19 +1742,19 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="Q14" t="n">
-        <v>1091</v>
+        <v>1215</v>
       </c>
       <c r="R14" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>891</v>
+        <v>1038</v>
       </c>
       <c r="T14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1754,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1766,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1190</v>
+        <v>1215</v>
       </c>
       <c r="AC14" t="n">
-        <v>1091</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="15">
@@ -1784,7 +1796,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1793,19 +1805,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="G15" t="n">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1823,25 +1835,25 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="Q15" t="n">
-        <v>404</v>
+        <v>435</v>
       </c>
       <c r="R15" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="S15" t="n">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1859,10 +1871,10 @@
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="AC15" t="n">
-        <v>404</v>
+        <v>435</v>
       </c>
     </row>
     <row r="16">
@@ -1886,76 +1898,76 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>815</v>
+        <v>275</v>
       </c>
       <c r="G16" t="n">
-        <v>1522</v>
+        <v>2176</v>
       </c>
       <c r="H16" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>516</v>
+      </c>
+      <c r="O16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>24</v>
-      </c>
-      <c r="L16" t="n">
-        <v>8</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>492</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
       <c r="P16" t="n">
-        <v>2921</v>
+        <v>3009</v>
       </c>
       <c r="Q16" t="n">
-        <v>2106</v>
+        <v>2734</v>
       </c>
       <c r="R16" t="n">
-        <v>815</v>
+        <v>276</v>
       </c>
       <c r="S16" t="n">
-        <v>1522</v>
+        <v>2176</v>
       </c>
       <c r="T16" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>516</v>
+      </c>
+      <c r="AA16" t="n">
         <v>4</v>
       </c>
-      <c r="W16" t="n">
-        <v>24</v>
-      </c>
-      <c r="X16" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>492</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3</v>
-      </c>
       <c r="AB16" t="n">
-        <v>2921</v>
+        <v>3009</v>
       </c>
       <c r="AC16" t="n">
-        <v>2106</v>
+        <v>2733</v>
       </c>
     </row>
   </sheetData>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA KHUSUS.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Kecamatan_KELUARGA KHUSUS.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,147 +417,147 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Kode Kecamatan</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Nama Kecamatan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Hasil Pendataan PPL</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>PENDATAAN K1 - Persentase Bangunan Keluarga Khusus Didata</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Persentase Bangunan Keluarga Khusus Didata</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
@@ -596,76 +584,76 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>643</v>
       </c>
       <c r="G2" t="n">
-        <v>3545</v>
+        <v>2752</v>
       </c>
       <c r="H2" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P2" t="n">
-        <v>4454</v>
+        <v>4258</v>
       </c>
       <c r="Q2" t="n">
-        <v>4424</v>
+        <v>3560</v>
       </c>
       <c r="R2" t="n">
-        <v>28</v>
+        <v>643</v>
       </c>
       <c r="S2" t="n">
-        <v>3533</v>
+        <v>2754</v>
       </c>
       <c r="T2" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
         <v>3</v>
       </c>
       <c r="Z2" t="n">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="AA2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AB2" t="n">
-        <v>4453</v>
+        <v>4258</v>
       </c>
       <c r="AC2" t="n">
-        <v>4423</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="3">
@@ -689,19 +677,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="G3" t="n">
-        <v>1112</v>
+        <v>857</v>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -713,31 +701,31 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>1513</v>
+        <v>1490</v>
       </c>
       <c r="Q3" t="n">
-        <v>1356</v>
+        <v>1107</v>
       </c>
       <c r="R3" t="n">
-        <v>52</v>
+        <v>184</v>
       </c>
       <c r="S3" t="n">
-        <v>1112</v>
+        <v>857</v>
       </c>
       <c r="T3" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="U3" t="n">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -749,16 +737,16 @@
         <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1513</v>
+        <v>1490</v>
       </c>
       <c r="AC3" t="n">
-        <v>1356</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="4">
@@ -773,85 +761,85 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>957</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4368</v>
+      </c>
+      <c r="H4" t="n">
+        <v>399</v>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="n">
+        <v>73</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>588</v>
+      </c>
+      <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>112</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5543</v>
-      </c>
-      <c r="H4" t="n">
-        <v>389</v>
-      </c>
-      <c r="I4" t="n">
-        <v>21</v>
-      </c>
-      <c r="J4" t="n">
-        <v>133</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>592</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
       <c r="P4" t="n">
-        <v>6795</v>
+        <v>6487</v>
       </c>
       <c r="Q4" t="n">
-        <v>6662</v>
+        <v>5430</v>
       </c>
       <c r="R4" t="n">
-        <v>113</v>
+        <v>959</v>
       </c>
       <c r="S4" t="n">
-        <v>5543</v>
+        <v>4368</v>
       </c>
       <c r="T4" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="U4" t="n">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="V4" t="n">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>6795</v>
+        <v>6487</v>
       </c>
       <c r="AC4" t="n">
-        <v>6661</v>
+        <v>5430</v>
       </c>
     </row>
     <row r="5">
@@ -875,76 +863,76 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="G5" t="n">
-        <v>3010</v>
+        <v>2276</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>3521</v>
+        <v>3306</v>
       </c>
       <c r="Q5" t="n">
-        <v>3521</v>
+        <v>2924</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="S5" t="n">
-        <v>3010</v>
+        <v>2276</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="X5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="AA5" t="n">
         <v>4</v>
       </c>
       <c r="AB5" t="n">
-        <v>3521</v>
+        <v>3306</v>
       </c>
       <c r="AC5" t="n">
-        <v>3521</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="6">
@@ -959,7 +947,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -968,76 +956,76 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="G6" t="n">
-        <v>952</v>
+        <v>694</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>1209</v>
+        <v>1158</v>
       </c>
       <c r="Q6" t="n">
-        <v>1100</v>
+        <v>832</v>
       </c>
       <c r="R6" t="n">
-        <v>102</v>
+        <v>310</v>
       </c>
       <c r="S6" t="n">
-        <v>952</v>
+        <v>694</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="n">
         <v>7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1209</v>
+        <v>1158</v>
       </c>
       <c r="AC6" t="n">
-        <v>1100</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7">
@@ -1052,25 +1040,25 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>280</v>
+      </c>
+      <c r="G7" t="n">
+        <v>644</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>47</v>
-      </c>
-      <c r="G7" t="n">
-        <v>912</v>
-      </c>
-      <c r="H7" t="n">
-        <v>17</v>
-      </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1085,28 +1073,28 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>1133</v>
+        <v>1065</v>
       </c>
       <c r="Q7" t="n">
-        <v>1086</v>
+        <v>784</v>
       </c>
       <c r="R7" t="n">
-        <v>47</v>
+        <v>280</v>
       </c>
       <c r="S7" t="n">
-        <v>912</v>
+        <v>644</v>
       </c>
       <c r="T7" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1121,16 +1109,16 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="AA7" t="n">
         <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1133</v>
+        <v>1065</v>
       </c>
       <c r="AC7" t="n">
-        <v>1086</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8">
@@ -1154,76 +1142,76 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>745</v>
+        <v>1630</v>
       </c>
       <c r="G8" t="n">
-        <v>3557</v>
+        <v>2443</v>
       </c>
       <c r="H8" t="n">
-        <v>205</v>
+        <v>289</v>
       </c>
       <c r="I8" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
         <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="O8" t="n">
         <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>5199</v>
+        <v>4810</v>
       </c>
       <c r="Q8" t="n">
-        <v>4402</v>
+        <v>3153</v>
       </c>
       <c r="R8" t="n">
-        <v>748</v>
+        <v>1630</v>
       </c>
       <c r="S8" t="n">
-        <v>3555</v>
+        <v>2443</v>
       </c>
       <c r="T8" t="n">
-        <v>204</v>
+        <v>289</v>
       </c>
       <c r="U8" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="V8" t="n">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="n">
         <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="AA8" t="n">
         <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>5199</v>
+        <v>4810</v>
       </c>
       <c r="AC8" t="n">
-        <v>4399</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="9">
@@ -1247,76 +1235,76 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>742</v>
+        <v>1980</v>
       </c>
       <c r="G9" t="n">
-        <v>4117</v>
+        <v>3260</v>
       </c>
       <c r="H9" t="n">
-        <v>780</v>
+        <v>296</v>
       </c>
       <c r="I9" t="n">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="J9" t="n">
-        <v>336</v>
+        <v>198</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>625</v>
+        <v>577</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6749</v>
+        <v>6348</v>
       </c>
       <c r="Q9" t="n">
-        <v>5894</v>
+        <v>4331</v>
       </c>
       <c r="R9" t="n">
-        <v>742</v>
+        <v>1980</v>
       </c>
       <c r="S9" t="n">
-        <v>4117</v>
+        <v>3260</v>
       </c>
       <c r="T9" t="n">
-        <v>780</v>
+        <v>295</v>
       </c>
       <c r="U9" t="n">
-        <v>113</v>
+        <v>37</v>
       </c>
       <c r="V9" t="n">
-        <v>335</v>
+        <v>198</v>
       </c>
       <c r="W9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>625</v>
+        <v>577</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>6749</v>
+        <v>6347</v>
       </c>
       <c r="AC9" t="n">
-        <v>5894</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="10">
@@ -1340,76 +1328,76 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>980</v>
+        <v>2620</v>
       </c>
       <c r="G10" t="n">
-        <v>6975</v>
+        <v>5034</v>
       </c>
       <c r="H10" t="n">
-        <v>281</v>
+        <v>48</v>
       </c>
       <c r="I10" t="n">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="J10" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>8991</v>
+        <v>8450</v>
       </c>
       <c r="Q10" t="n">
-        <v>7916</v>
+        <v>5652</v>
       </c>
       <c r="R10" t="n">
-        <v>981</v>
+        <v>2620</v>
       </c>
       <c r="S10" t="n">
-        <v>6975</v>
+        <v>5034</v>
       </c>
       <c r="T10" t="n">
-        <v>280</v>
+        <v>48</v>
       </c>
       <c r="U10" t="n">
-        <v>95</v>
+        <v>176</v>
       </c>
       <c r="V10" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
         <v>2</v>
       </c>
       <c r="Z10" t="n">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB10" t="n">
-        <v>8991</v>
+        <v>8448</v>
       </c>
       <c r="AC10" t="n">
-        <v>7915</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="11">
@@ -1424,7 +1412,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1433,76 +1421,76 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>432</v>
+        <v>1416</v>
       </c>
       <c r="G11" t="n">
-        <v>4389</v>
+        <v>3241</v>
       </c>
       <c r="H11" t="n">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="I11" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J11" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>6</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P11" t="n">
-        <v>5634</v>
+        <v>5361</v>
       </c>
       <c r="Q11" t="n">
-        <v>5057</v>
+        <v>3797</v>
       </c>
       <c r="R11" t="n">
-        <v>434</v>
+        <v>1418</v>
       </c>
       <c r="S11" t="n">
-        <v>4389</v>
+        <v>3241</v>
       </c>
       <c r="T11" t="n">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="U11" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="V11" t="n">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="W11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>6</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>5634</v>
+        <v>5361</v>
       </c>
       <c r="AC11" t="n">
-        <v>5055</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="12">
@@ -1526,22 +1514,22 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>174</v>
+        <v>751</v>
       </c>
       <c r="G12" t="n">
-        <v>1652</v>
+        <v>1250</v>
       </c>
       <c r="H12" t="n">
-        <v>152</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="J12" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>7</v>
@@ -1550,34 +1538,34 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>2485</v>
+        <v>2445</v>
       </c>
       <c r="Q12" t="n">
-        <v>2257</v>
+        <v>1608</v>
       </c>
       <c r="R12" t="n">
-        <v>174</v>
+        <v>751</v>
       </c>
       <c r="S12" t="n">
-        <v>1652</v>
+        <v>1248</v>
       </c>
       <c r="T12" t="n">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="U12" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="V12" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="W12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>7</v>
@@ -1586,16 +1574,16 @@
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="AA12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AB12" t="n">
-        <v>2485</v>
+        <v>2445</v>
       </c>
       <c r="AC12" t="n">
-        <v>2257</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="13">
@@ -1619,76 +1607,76 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>149</v>
+        <v>1393</v>
       </c>
       <c r="G13" t="n">
-        <v>8976</v>
+        <v>7134</v>
       </c>
       <c r="H13" t="n">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="I13" t="n">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="O13" t="n">
         <v>14</v>
       </c>
       <c r="P13" t="n">
-        <v>10379</v>
+        <v>9735</v>
       </c>
       <c r="Q13" t="n">
-        <v>10172</v>
+        <v>8195</v>
       </c>
       <c r="R13" t="n">
-        <v>149</v>
+        <v>1394</v>
       </c>
       <c r="S13" t="n">
-        <v>8976</v>
+        <v>7134</v>
       </c>
       <c r="T13" t="n">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="U13" t="n">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="V13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="AA13" t="n">
         <v>14</v>
       </c>
       <c r="AB13" t="n">
-        <v>10379</v>
+        <v>9735</v>
       </c>
       <c r="AC13" t="n">
-        <v>10171</v>
+        <v>8195</v>
       </c>
     </row>
     <row r="14">
@@ -1712,13 +1700,13 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G14" t="n">
-        <v>1038</v>
+        <v>891</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1730,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1742,19 +1730,19 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1215</v>
+        <v>1190</v>
       </c>
       <c r="Q14" t="n">
-        <v>1215</v>
+        <v>1091</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="S14" t="n">
-        <v>1038</v>
+        <v>891</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1766,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1778,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1215</v>
+        <v>1190</v>
       </c>
       <c r="AC14" t="n">
-        <v>1215</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="15">
@@ -1796,7 +1784,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1805,19 +1793,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="G15" t="n">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1835,25 +1823,25 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="Q15" t="n">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="R15" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="S15" t="n">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -1871,10 +1859,10 @@
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="AC15" t="n">
-        <v>435</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16">
@@ -1898,76 +1886,76 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>275</v>
+        <v>815</v>
       </c>
       <c r="G16" t="n">
-        <v>2176</v>
+        <v>1522</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L16" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2921</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2106</v>
+      </c>
+      <c r="R16" t="n">
+        <v>815</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1522</v>
+      </c>
+      <c r="T16" t="n">
+        <v>53</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
         <v>4</v>
       </c>
-      <c r="P16" t="n">
-        <v>3009</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2734</v>
-      </c>
-      <c r="R16" t="n">
-        <v>276</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2176</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>10</v>
-      </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="AA16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>3009</v>
+        <v>2921</v>
       </c>
       <c r="AC16" t="n">
-        <v>2733</v>
+        <v>2106</v>
       </c>
     </row>
   </sheetData>
